--- a/data/trans_orig/P36B15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B15-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202253</t>
+          <t>201353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>253839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200742</t>
+          <t>201361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255958</t>
+          <t>255230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416557</t>
+          <t>414693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>489993</t>
+          <t>491259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163289</t>
+          <t>164271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213521</t>
+          <t>213361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263616</t>
+          <t>262115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322899</t>
+          <t>321515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440514</t>
+          <t>441634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518806</t>
+          <t>519996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272060</t>
+          <t>270592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329901</t>
+          <t>328482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>355721</t>
+          <t>355880</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>422840</t>
+          <t>423172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>644021</t>
+          <t>639737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>726756</t>
+          <t>726086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162424</t>
+          <t>162194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213679</t>
+          <t>214900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>207468</t>
+          <t>209191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>264873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384401</t>
+          <t>386051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>455786</t>
+          <t>460313</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109665</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149751</t>
+          <t>151673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143030</t>
+          <t>142756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193648</t>
+          <t>191546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>266640</t>
+          <t>261389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328514</t>
+          <t>324054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164704</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217933</t>
+          <t>217380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141452</t>
+          <t>142676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191756</t>
+          <t>190243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320286</t>
+          <t>325037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392510</t>
+          <t>394992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326397</t>
+          <t>325460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>395138</t>
+          <t>393403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278308</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343885</t>
+          <t>342622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626999</t>
+          <t>623241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>716503</t>
+          <t>713148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>462149</t>
+          <t>461274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>539230</t>
+          <t>540629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>511331</t>
+          <t>509233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587554</t>
+          <t>582433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>990225</t>
+          <t>997951</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1101770</t>
+          <t>1097462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>343396</t>
+          <t>342400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>414026</t>
+          <t>409214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283980</t>
+          <t>287609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>349733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642296</t>
+          <t>647228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>737228</t>
+          <t>738497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237774</t>
+          <t>234880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>297022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217642</t>
+          <t>213505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276640</t>
+          <t>273448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465891</t>
+          <t>462212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>545703</t>
+          <t>547438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98710</t>
+          <t>96402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>43177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74071</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>114873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160844</t>
+          <t>160598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93566</t>
+          <t>94799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134972</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71974</t>
+          <t>71962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105242</t>
+          <t>105825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175798</t>
+          <t>176575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>230753</t>
+          <t>228085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153854</t>
+          <t>154315</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197919</t>
+          <t>198273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>149615</t>
+          <t>151872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190791</t>
+          <t>194932</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>315246</t>
+          <t>317130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>378508</t>
+          <t>379124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96978</t>
+          <t>95947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>135234</t>
+          <t>135214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83881</t>
+          <t>82631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118643</t>
+          <t>120186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190398</t>
+          <t>189242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242311</t>
+          <t>240941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51846</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84387</t>
+          <t>85329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76361</t>
+          <t>74392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105532</t>
+          <t>106122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150096</t>
+          <t>150276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>455630</t>
+          <t>456201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>534601</t>
+          <t>541056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>410761</t>
+          <t>412721</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>493858</t>
+          <t>493454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>887323</t>
+          <t>883487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1003786</t>
+          <t>1000390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616882</t>
+          <t>615436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>708048</t>
+          <t>706450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>643315</t>
+          <t>646323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>740202</t>
+          <t>735504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282821</t>
+          <t>1282246</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1423548</t>
+          <t>1418252</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>926365</t>
+          <t>927545</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1030141</t>
+          <t>1031090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1049852</t>
+          <t>1046844</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1161508</t>
+          <t>1162633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2001536</t>
+          <t>2007927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2150950</t>
+          <t>2156425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>628331</t>
+          <t>625674</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>724893</t>
+          <t>722456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>608564</t>
+          <t>605972</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>699786</t>
+          <t>691993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1263737</t>
+          <t>1267105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1398345</t>
+          <t>1393132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>418716</t>
+          <t>421621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>500709</t>
+          <t>495915</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>428352</t>
+          <t>427900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>508315</t>
+          <t>509827</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>874278</t>
+          <t>872703</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>983971</t>
+          <t>984167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>190743</t>
+          <t>186480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>243818</t>
+          <t>243250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227694</t>
+          <t>229424</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287960</t>
+          <t>286328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>436217</t>
+          <t>436969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>509575</t>
+          <t>516449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104317</t>
+          <t>105706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147589</t>
+          <t>150371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>184950</t>
+          <t>184228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237984</t>
+          <t>238823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301333</t>
+          <t>302074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>371317</t>
+          <t>370684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>211198</t>
+          <t>212877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267722</t>
+          <t>266541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>327144</t>
+          <t>326706</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>392010</t>
+          <t>391445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>557972</t>
+          <t>555282</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642807</t>
+          <t>644335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195260</t>
+          <t>193151</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250253</t>
+          <t>249322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>248152</t>
+          <t>252668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>310922</t>
+          <t>314376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459178</t>
+          <t>461206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542160</t>
+          <t>540418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>139047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186399</t>
+          <t>184955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196560</t>
+          <t>193902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>249459</t>
+          <t>252977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349055</t>
+          <t>344969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417691</t>
+          <t>419641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212244</t>
+          <t>210130</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274370</t>
+          <t>271418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167287</t>
+          <t>167206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220427</t>
+          <t>223566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>392058</t>
+          <t>392670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>477381</t>
+          <t>475354</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226682</t>
+          <t>231325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289920</t>
+          <t>287907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211387</t>
+          <t>211398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270686</t>
+          <t>272589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459032</t>
+          <t>457219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540793</t>
+          <t>542216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>489187</t>
+          <t>490457</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>574093</t>
+          <t>573042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>476169</t>
+          <t>473212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>551266</t>
+          <t>553813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>984029</t>
+          <t>989915</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1095529</t>
+          <t>1100355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>491146</t>
+          <t>492357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>575605</t>
+          <t>580011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>432414</t>
+          <t>430345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509426</t>
+          <t>510268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>948743</t>
+          <t>948341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1060233</t>
+          <t>1056365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363255</t>
+          <t>361273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435744</t>
+          <t>435266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305067</t>
+          <t>302034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371433</t>
+          <t>368454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>685584</t>
+          <t>688553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783846</t>
+          <t>785124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74466</t>
+          <t>73872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>61947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85966</t>
+          <t>85889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127017</t>
+          <t>126742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5169,47 +5169,47 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>53194</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>87259</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>71023</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>55535</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>87834</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>71023</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>56064</t>
-        </is>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89709</t>
+          <t>88893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>117330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165387</t>
+          <t>165653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144917</t>
+          <t>141453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185431</t>
+          <t>189156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>121833</t>
+          <t>120623</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162344</t>
+          <t>162619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>276284</t>
+          <t>276580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>338995</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>100671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>141270</t>
+          <t>139129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106954</t>
+          <t>104798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>146681</t>
+          <t>145375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>214502</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275159</t>
+          <t>272598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>86267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92387</t>
+          <t>90654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118993</t>
+          <t>121348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166884</t>
+          <t>167017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>467832</t>
+          <t>469555</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>557672</t>
+          <t>554629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>457620</t>
+          <t>458452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>543716</t>
+          <t>542763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>948948</t>
+          <t>946215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1072722</t>
+          <t>1072233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>414069</t>
+          <t>412537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>498586</t>
+          <t>495010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>479292</t>
+          <t>479433</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>568101</t>
+          <t>566718</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>916693</t>
+          <t>916542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1039546</t>
+          <t>1036111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>883906</t>
+          <t>882897</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>987525</t>
+          <t>993846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>956551</t>
+          <t>953859</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1067236</t>
+          <t>1065561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1863556</t>
+          <t>1870561</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2021498</t>
+          <t>2020405</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>823702</t>
+          <t>824231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>925827</t>
+          <t>927922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>814161</t>
+          <t>820300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>925849</t>
+          <t>929614</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1674036</t>
+          <t>1675461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1831613</t>
+          <t>1826535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>583467</t>
+          <t>582863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>678646</t>
+          <t>677047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>585392</t>
+          <t>589232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>678203</t>
+          <t>676051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1198743</t>
+          <t>1194503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1333478</t>
+          <t>1326339</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>202372</t>
+          <t>203202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255607</t>
+          <t>250688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>282714</t>
+          <t>283922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>343803</t>
+          <t>344214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>498488</t>
+          <t>501427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580837</t>
+          <t>582563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118336</t>
+          <t>119451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159355</t>
+          <t>160186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175728</t>
+          <t>176362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226024</t>
+          <t>229843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309492</t>
+          <t>306861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375033</t>
+          <t>375671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142158</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184506</t>
+          <t>186367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>194991</t>
+          <t>195637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249115</t>
+          <t>249988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>353534</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>419446</t>
+          <t>419542</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124925</t>
+          <t>122775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>167394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148389</t>
+          <t>148367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199603</t>
+          <t>198635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286760</t>
+          <t>283181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>351149</t>
+          <t>346738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64403</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100539</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>69807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107297</t>
+          <t>105279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141062</t>
+          <t>141030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>196239</t>
+          <t>190266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>302306</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>372135</t>
+          <t>369433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>292968</t>
+          <t>291357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359421</t>
+          <t>359042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>613561</t>
+          <t>609575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706936</t>
+          <t>710689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365111</t>
+          <t>363916</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436778</t>
+          <t>437820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>345319</t>
+          <t>341508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412055</t>
+          <t>410619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>726719</t>
+          <t>729550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>831670</t>
+          <t>840154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>505909</t>
+          <t>508153</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>588567</t>
+          <t>587482</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>503861</t>
+          <t>501539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>582582</t>
+          <t>583615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1028341</t>
+          <t>1036668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1146571</t>
+          <t>1150930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>466014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>543223</t>
+          <t>546196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>428481</t>
+          <t>430476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>504673</t>
+          <t>503192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>919895</t>
+          <t>913612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1022743</t>
+          <t>1023788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254050</t>
+          <t>253022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320176</t>
+          <t>316693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244984</t>
+          <t>243533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>305812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>514231</t>
+          <t>516393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>604570</t>
+          <t>601619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>79863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119673</t>
+          <t>117771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48845</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81458</t>
+          <t>81946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139021</t>
+          <t>139694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186968</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80795</t>
+          <t>80110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119352</t>
+          <t>118510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103629</t>
+          <t>102828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142404</t>
+          <t>141648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195118</t>
+          <t>195062</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249136</t>
+          <t>247961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153338</t>
+          <t>156985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200468</t>
+          <t>202470</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154105</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>280619</t>
+          <t>277652</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>342694</t>
+          <t>339888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>103991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140121</t>
+          <t>143342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136080</t>
+          <t>134245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>180383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>250703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309610</t>
+          <t>310695</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66516</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57252</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88554</t>
+          <t>88318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>102380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142884</t>
+          <t>143159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>618220</t>
+          <t>614242</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>712209</t>
+          <t>706876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>650702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>750810</t>
+          <t>748728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1293274</t>
+          <t>1298659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1430610</t>
+          <t>1431202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>593434</t>
+          <t>594054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>686379</t>
+          <t>686946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,82 +8825,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>699889</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>652812</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>752768</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1338956</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1269427</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1405388</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>20,39%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>699889</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>650738</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>747229</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1338956</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1271208</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1403617</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>835648</t>
+          <t>829335</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>938177</t>
+          <t>939337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846187</t>
+          <t>843090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>952778</t>
+          <t>948484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1710054</t>
+          <t>1711663</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1858302</t>
+          <t>1852239</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>721492</t>
+          <t>717256</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>818915</t>
+          <t>825361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>750031</t>
+          <t>742418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>849927</t>
+          <t>844009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1493157</t>
+          <t>1492230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1635593</t>
+          <t>1633036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>375845</t>
+          <t>374779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>456795</t>
+          <t>454526</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>396007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>470555</t>
+          <t>472927</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>788838</t>
+          <t>788645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>895825</t>
+          <t>900134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>174775</t>
+          <t>200076</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155540</t>
+          <t>179381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>195426</t>
+          <t>221428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>287873</t>
+          <t>310487</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268334</t>
+          <t>289295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308602</t>
+          <t>332137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>462649</t>
+          <t>510563</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>433741</t>
+          <t>477557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490521</t>
+          <t>538907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114490</t>
+          <t>126400</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>107558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132334</t>
+          <t>147679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>169513</t>
+          <t>184780</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152543</t>
+          <t>167562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187532</t>
+          <t>203444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,27 +9788,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>284003</t>
+          <t>311179</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258229</t>
+          <t>286957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>311273</t>
+          <t>343282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124203</t>
+          <t>139629</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106986</t>
+          <t>119811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142855</t>
+          <t>161197</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>179088</t>
+          <t>195892</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>178510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198815</t>
+          <t>216099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>303291</t>
+          <t>335520</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>279295</t>
+          <t>308764</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>332770</t>
+          <t>365702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54865</t>
+          <t>58263</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>44768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72841</t>
+          <t>76680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67229</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>62882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>122093</t>
+          <t>132822</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104076</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143385</t>
+          <t>156062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>39338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57549</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,17 +10092,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>53988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40152</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>105714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79195</t>
+          <t>89276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>125096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>512629</t>
+          <t>576093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>512629</t>
+          <t>576093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512629</t>
+          <t>576093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819706</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819706</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>753334</t>
+          <t>819706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1265963</t>
+          <t>1395799</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1265963</t>
+          <t>1395799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1265963</t>
+          <t>1395799</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>518333</t>
+          <t>574179</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>342099</t>
+          <t>530118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>598366</t>
+          <t>619172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>516726</t>
+          <t>576694</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375295</t>
+          <t>540967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>592671</t>
+          <t>617326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1035059</t>
+          <t>1150873</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>826183</t>
+          <t>1098857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1157934</t>
+          <t>1214843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>495970</t>
+          <t>537371</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326963</t>
+          <t>493751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576383</t>
+          <t>583764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>721866</t>
+          <t>582636</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553309</t>
+          <t>549942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1153075</t>
+          <t>623799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1217836</t>
+          <t>1120007</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1006927</t>
+          <t>1056619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1709863</t>
+          <t>1177822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>627123</t>
+          <t>668006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>436779</t>
+          <t>618377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>725691</t>
+          <t>718641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>639893</t>
+          <t>629393</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>473042</t>
+          <t>590184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>772359</t>
+          <t>668132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1267016</t>
+          <t>1297398</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1022377</t>
+          <t>1235193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1432137</t>
+          <t>1360886</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>255972</t>
+          <t>279840</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177468</t>
+          <t>246454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305896</t>
+          <t>317150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>190333</t>
+          <t>227379</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136325</t>
+          <t>202145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>225832</t>
+          <t>256995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>446305</t>
+          <t>507219</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>362209</t>
+          <t>464360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515377</t>
+          <t>558464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>391809</t>
+          <t>168612</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152316</t>
+          <t>140613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1030366</t>
+          <t>205958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>166554</t>
+          <t>152607</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118732</t>
+          <t>130617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281461</t>
+          <t>178740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>558363</t>
+          <t>321219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310107</t>
+          <t>286927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1328383</t>
+          <t>366072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2289208</t>
+          <t>2228008</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2289208</t>
+          <t>2228008</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2289208</t>
+          <t>2228008</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235372</t>
+          <t>2168709</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235372</t>
+          <t>2168709</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235372</t>
+          <t>2168709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524580</t>
+          <t>4396716</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524580</t>
+          <t>4396716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524580</t>
+          <t>4396716</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>219844</t>
+          <t>244079</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>195051</t>
+          <t>217814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243390</t>
+          <t>271458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>227957</t>
+          <t>249885</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>206397</t>
+          <t>227553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249656</t>
+          <t>273593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>447801</t>
+          <t>493964</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416727</t>
+          <t>457467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482120</t>
+          <t>528490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177249</t>
+          <t>194456</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152869</t>
+          <t>169453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203000</t>
+          <t>223502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>178422</t>
+          <t>197887</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160824</t>
+          <t>177193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197369</t>
+          <t>220767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355671</t>
+          <t>392343</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325161</t>
+          <t>356745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387123</t>
+          <t>426243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>160163</t>
+          <t>178553</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138534</t>
+          <t>154400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185060</t>
+          <t>202261</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>178177</t>
+          <t>197666</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158511</t>
+          <t>177598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200064</t>
+          <t>221085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>338340</t>
+          <t>376219</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>310053</t>
+          <t>342748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>371256</t>
+          <t>412309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>59698</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43383</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88057</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56481</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>103537</t>
+          <t>109716</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81611</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133775</t>
+          <t>133315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>38761</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23089</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43457</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>60744</t>
+          <t>72717</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47384</t>
+          <t>58546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645789</t>
+          <t>710742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734217</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734217</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660304</t>
+          <t>734217</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306093</t>
+          <t>1444958</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306093</t>
+          <t>1444958</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306093</t>
+          <t>1444958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>912951</t>
+          <t>1018334</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>699194</t>
+          <t>961195</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1001647</t>
+          <t>1079989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,67 +11686,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1032557</t>
+          <t>1137065</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>856467</t>
+          <t>1089166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1124182</t>
+          <t>1185091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2155399</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2079821</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2229886</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>30,81%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2934</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1945508</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1650097</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2094311</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>787709</t>
+          <t>858227</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598966</t>
+          <t>802872</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>871735</t>
+          <t>916250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1069801</t>
+          <t>965303</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>891049</t>
+          <t>917211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1536034</t>
+          <t>1010297</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1857509</t>
+          <t>1823530</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1650453</t>
+          <t>1753538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2364857</t>
+          <t>1900995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>911489</t>
+          <t>986187</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>709996</t>
+          <t>928008</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1002245</t>
+          <t>1051024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>997159</t>
+          <t>1022950</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848134</t>
+          <t>971757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1139861</t>
+          <t>1076692</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1908648</t>
+          <t>2009137</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1661796</t>
+          <t>1931688</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2102139</t>
+          <t>2090954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>370859</t>
+          <t>397801</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>288009</t>
+          <t>354243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>428253</t>
+          <t>444747</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>301076</t>
+          <t>351956</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>244302</t>
+          <t>317351</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340279</t>
+          <t>385164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>671935</t>
+          <t>749757</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>580961</t>
+          <t>693393</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>743569</t>
+          <t>807366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>464617</t>
+          <t>254293</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>228327</t>
+          <t>217621</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1255572</t>
+          <t>298728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>248418</t>
+          <t>245357</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>201200</t>
+          <t>217830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>366988</t>
+          <t>275778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>713035</t>
+          <t>499650</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>459778</t>
+          <t>456935</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1510703</t>
+          <t>554670</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3447625</t>
+          <t>3514842</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3447625</t>
+          <t>3514842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3447625</t>
+          <t>3514842</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3649010</t>
+          <t>3722631</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3649010</t>
+          <t>3722631</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3649010</t>
+          <t>3722631</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7096635</t>
+          <t>7237473</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7096635</t>
+          <t>7237473</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7096635</t>
+          <t>7237473</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
